--- a/test-results.xlsx
+++ b/test-results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
   <si>
     <t>Test Title</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>A test expected to fail @report</t>
-  </si>
-  <si>
-    <t>failed</t>
   </si>
   <si>
     <t xml:space="preserve">Error: [2mexpect([22m[31mpage[39m[2m).[22mtoHaveTitle[2m([22m[32mexpected[39m[2m)[22m failed
@@ -485,7 +482,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>621</v>
+        <v>515</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -499,7 +496,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>15189</v>
+        <v>6036</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -513,7 +510,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>19015</v>
+        <v>10049</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -527,7 +524,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>1253</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -541,7 +538,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>9706</v>
+        <v>8124</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -555,7 +552,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>30463</v>
+        <v>19887</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -569,7 +566,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>5313</v>
+        <v>4995</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -580,18 +577,18 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>11421</v>
+      </c>
+      <c r="D9" t="s">
         <v>15</v>
-      </c>
-      <c r="C9">
-        <v>12906</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -605,13 +602,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
       <c r="C11">
-        <v>5331</v>
+        <v>5415</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
@@ -619,13 +616,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12">
-        <v>8351</v>
+        <v>8558</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
